--- a/Experiments/DetectEvent/data/p06_visual_pick_gougeevents_merged.xlsx
+++ b/Experiments/DetectEvent/data/p06_visual_pick_gougeevents_merged.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kokubo/Dropbox/NIED_RESEARCH/4mBIAX_submission/4mNonSelfSim_Paper/Experiments/DetectEvent/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kokubo/Dropbox/NIED_RESEARCH/4mBIAX_submission/4mNonSelfSim_Paper_v2/Experiments/DetectEvent/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F49414-7B18-6344-8A86-C484A4F15599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE2FEF9-E03E-9046-9108-0326FCE988DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3080" windowWidth="28740" windowHeight="21160" xr2:uid="{CAF4AC9E-8B8C-5842-900A-3EB882FF1CD6}"/>
+    <workbookView xWindow="1980" yWindow="520" windowWidth="28740" windowHeight="19920" xr2:uid="{CAF4AC9E-8B8C-5842-900A-3EB882FF1CD6}"/>
   </bookViews>
   <sheets>
     <sheet name="p06_visual_pick_gougeevents_mer" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">p06_visual_pick_gougeevents_mer!$A$1:$I$138</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -4834,5 +4837,6 @@
     <sortCondition ref="D6:D139"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>